--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486759_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486759_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. KELLIER</t>
+          <t>G. MUKENDI KABANGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4043</v>
+        <v>4.5819</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3955</v>
+        <v>2.6243</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0089</v>
+        <v>1.9576</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2899</v>
+        <v>3.3239</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8347</v>
+        <v>3.8145</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5448</v>
+        <v>-0.4906</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6495</v>
+        <v>2.8904</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5251</v>
+        <v>2.8497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1244</v>
+        <v>0.0407</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3596</v>
+        <v>0.4335</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6904</v>
+        <v>0.9648</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6692</v>
+        <v>-0.5313</v>
       </c>
       <c r="P2" t="n">
         <v>-0.5792</v>
@@ -610,28 +610,28 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5086</v>
+        <v>0.9378</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2061</v>
+        <v>0.1514</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3025</v>
+        <v>0.7864</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1851</v>
+        <v>0.8995</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4707</v>
+        <v>1.5133</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>G. MUKENDI KABANGA</t>
+          <t>J. KELLIER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0231</v>
+        <v>4.4197</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1897</v>
+        <v>4.1061</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8335</v>
+        <v>0.3136</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3239</v>
+        <v>2.2899</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8145</v>
+        <v>2.8347</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4906</v>
+        <v>-0.5448</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8904</v>
+        <v>3.6495</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8497</v>
+        <v>3.5251</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>0.1244</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4335</v>
+        <v>-1.3596</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9648</v>
+        <v>-0.6904</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5313</v>
+        <v>-0.6692</v>
       </c>
       <c r="P3" t="n">
         <v>-0.5792</v>
@@ -688,28 +688,28 @@
         <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>1.379</v>
+        <v>1.524</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7168</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6622</v>
+        <v>0.6072</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8995</v>
+        <v>1.1851</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5133</v>
+        <v>1.4707</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CASTELANOS POLA</t>
+          <t>P. LOPEZ USO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4301</v>
+        <v>3.6632</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6983</v>
+        <v>2.639</v>
       </c>
       <c r="F4" t="n">
-        <v>2.7318</v>
+        <v>1.0241</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3195</v>
+        <v>3.1902</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3376</v>
+        <v>2.4826</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0181</v>
+        <v>0.7076</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0928</v>
+        <v>2.7633</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4417</v>
+        <v>1.3797</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6511</v>
+        <v>1.3835</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2268</v>
+        <v>0.4269</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8959</v>
+        <v>1.1029</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6692</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7325</v>
+        <v>0.1794</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1928</v>
+        <v>-0.1242</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5396</v>
+        <v>0.3036</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6565</v>
+        <v>-0.2856</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. LOPEZ USO</t>
+          <t>J. VAQUERO PASCUAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2522</v>
+        <v>3.5506</v>
       </c>
       <c r="E5" t="n">
-        <v>2.377</v>
+        <v>2.3585</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8752</v>
+        <v>1.1921</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1902</v>
+        <v>1.8304</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4826</v>
+        <v>2.5718</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7076</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7633</v>
+        <v>2.4315</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3797</v>
+        <v>2.5038</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3835</v>
+        <v>-0.0722</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4269</v>
+        <v>-0.6011</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1029</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6692</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2316</v>
+        <v>0.7861</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3863</v>
+        <v>0.3445</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1546</v>
+        <v>0.4416</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2856</v>
+        <v>1.5133</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. VAQUERO PASCUAL</t>
+          <t>A. CASTELANOS POLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0403</v>
+        <v>2.7322</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0965</v>
+        <v>0.5467</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9438</v>
+        <v>2.1855</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8304</v>
+        <v>3.3195</v>
       </c>
       <c r="H6" t="n">
-        <v>2.5718</v>
+        <v>3.3376</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.0181</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4315</v>
+        <v>3.0928</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5038</v>
+        <v>2.4417</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0722</v>
+        <v>0.6511</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6011</v>
+        <v>0.2268</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.8959</v>
       </c>
       <c r="O6" t="n">
         <v>-0.6692</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2758</v>
+        <v>1.0345</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0825</v>
+        <v>0.0412</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1933</v>
+        <v>0.9933</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5133</v>
+        <v>-0.6565</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>-0.6565</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1045</v>
+        <v>2.6479</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7802</v>
+        <v>1.249</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3244</v>
+        <v>1.3989</v>
       </c>
       <c r="G7" t="n">
         <v>4.3717</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0498</v>
+        <v>0.5931</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6622</v>
+        <v>-0.1933</v>
       </c>
       <c r="U7" t="n">
-        <v>0.712</v>
+        <v>0.7865</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. OLIVA I CAMPABADAL</t>
+          <t>J. SOLA ARGEMI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6078</v>
+        <v>1.0257</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1451</v>
+        <v>1.657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4628</v>
+        <v>-0.6314</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.469</v>
+        <v>-0.8982</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6274</v>
+        <v>1.4755</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0964</v>
+        <v>-2.3737</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0074</v>
+        <v>1.1441</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3864</v>
+        <v>2.4417</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.379</v>
+        <v>-1.2976</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4764</v>
+        <v>-2.0423</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.759</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2826</v>
+        <v>-1.0761</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8991</v>
+        <v>0.3792</v>
       </c>
       <c r="T8" t="n">
-        <v>1.103</v>
+        <v>0.2273</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.204</v>
+        <v>0.1519</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3709</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3709</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SAEZ PALOMINO</t>
+          <t>J. KASA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.182</v>
+        <v>0.5858</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1104</v>
+        <v>1.1313</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2923</v>
+        <v>-0.5456</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2758</v>
+        <v>-0.7245</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2758</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.1514</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.8419</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.1862</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2758</v>
+        <v>-1.5664</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2758</v>
+        <v>-0.7593</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.8071</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.09379999999999999</v>
+        <v>0.3449</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1104</v>
+        <v>0.2894</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0166</v>
+        <v>0.0554</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLA ARGEMI</t>
+          <t>M. OLIVA I CAMPABADAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.0266</v>
+        <v>0.3983</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8779</v>
+        <v>-0.2134</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9045</v>
+        <v>0.6117</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8982</v>
+        <v>-0.469</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4755</v>
+        <v>0.6274</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3737</v>
+        <v>-1.0964</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1441</v>
+        <v>0.0074</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4417</v>
+        <v>1.3864</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2976</v>
+        <v>-1.379</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0423</v>
+        <v>-0.4764</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.759</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0761</v>
+        <v>0.2826</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5446</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.673</v>
+        <v>0.6895</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5518</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1212</v>
+        <v>-0.055</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. KASA</t>
+          <t>J. SAEZ PALOMINO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.08989999999999999</v>
+        <v>0.2068</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4556</v>
+        <v>-0.1104</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5456</v>
+        <v>0.3172</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7245</v>
+        <v>0.2758</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5731000000000001</v>
+        <v>0.2758</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1514</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8419</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1862</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6556999999999999</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5664</v>
+        <v>0.2758</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7593</v>
+        <v>0.2758</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8071</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3309</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3863</v>
+        <v>-0.1104</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0554</v>
+        <v>0.0414</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1354</v>
+        <v>0.0177</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0897</v>
+        <v>0.0137</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0457</v>
+        <v>0.0039</v>
       </c>
       <c r="G12" t="n">
         <v>0.2275</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.0231</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1354</v>
+        <v>-1.7699</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1123</v>
+        <v>1.2613</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8759</v>
@@ -1468,13 +1468,13 @@
         <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2316</v>
+        <v>0.2828</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4415</v>
+        <v>-0.076</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2098</v>
+        <v>0.3588</v>
       </c>
       <c r="V13" t="n">
         <v>0.8568</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>22.7693</v>
+        <v>23.3212</v>
       </c>
       <c r="E14" t="n">
-        <v>13.6803</v>
+        <v>14.2319</v>
       </c>
       <c r="F14" t="n">
-        <v>9.089199999999998</v>
+        <v>9.088899999999999</v>
       </c>
       <c r="G14" t="n">
         <v>15.8613</v>
@@ -1528,16 +1528,16 @@
         <v>1.8655</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.6642</v>
+        <v>-5.664199999999999</v>
       </c>
       <c r="N14" t="n">
         <v>1.0276</v>
       </c>
       <c r="O14" t="n">
-        <v>-6.6918</v>
+        <v>-6.691799999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.8961</v>
+        <v>-2.896100000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.481</v>
@@ -1546,10 +1546,10 @@
         <v>11.5845</v>
       </c>
       <c r="S14" t="n">
-        <v>6.206599999999999</v>
+        <v>6.7581</v>
       </c>
       <c r="T14" t="n">
-        <v>1.652300000000001</v>
+        <v>2.2043</v>
       </c>
       <c r="U14" t="n">
         <v>4.553900000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3435</v>
+        <v>1.4966</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5968</v>
+        <v>0.7002</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7468</v>
+        <v>0.7964</v>
       </c>
       <c r="G15" t="n">
         <v>0.41</v>
@@ -1624,13 +1624,13 @@
         <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0978</v>
+        <v>-0.9447</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6347</v>
+        <v>-0.5312</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4632</v>
+        <v>-0.4135</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2856</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1866</v>
+        <v>0.3894</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0683</v>
+        <v>0.1717</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1183</v>
+        <v>0.2177</v>
       </c>
       <c r="G16" t="n">
         <v>0.406</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1269</v>
+        <v>0.0759</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0552</v>
+        <v>0.0482</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0717</v>
+        <v>0.0277</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2856</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2045</v>
+        <v>-0.1259</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.8711</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9722</v>
+        <v>-0.997</v>
       </c>
       <c r="G17" t="n">
         <v>1.1388</v>
@@ -1780,13 +1780,13 @@
         <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2854</v>
+        <v>-1.2068</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9657</v>
+        <v>-0.8623</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3196</v>
+        <v>-0.3445</v>
       </c>
       <c r="V17" t="n">
         <v>0.3282</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3246</v>
+        <v>-1.0681</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8342000000000001</v>
+        <v>-0.6274</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4904</v>
+        <v>-0.4407</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3166</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6565</v>
+        <v>-0.4</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0495</v>
+        <v>0.0002</v>
       </c>
       <c r="V18" t="n">
         <v>1.2277</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>D. MARTINEZ DE LA SERNA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8334</v>
+        <v>-2.7441</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4707</v>
+        <v>-1.0483</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3626</v>
+        <v>-1.6958</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6165</v>
+        <v>-1.3247</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2412</v>
+        <v>-0.9313</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3753</v>
+        <v>-0.3934</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4052</v>
+        <v>0.1035</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9319</v>
+        <v>0.1035</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5266999999999999</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.0217</v>
+        <v>-1.4282</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.1732</v>
+        <v>-1.0348</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1514</v>
+        <v>-0.3934</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3515</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3169</v>
+        <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7116</v>
+        <v>-0.269</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9106</v>
+        <v>-0.1864</v>
       </c>
       <c r="U19" t="n">
-        <v>0.199</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8568</v>
+        <v>-0.5712</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8568</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. MARTINEZ DE LA SERNA</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.253</v>
+        <v>-2.9286</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3586</v>
+        <v>-1.3673</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8945</v>
+        <v>-1.5613</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3247</v>
+        <v>-2.6165</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9313</v>
+        <v>-2.2412</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3934</v>
+        <v>-0.3753</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1035</v>
+        <v>0.4052</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1035</v>
+        <v>0.9319</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4282</v>
+        <v>-3.0217</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0348</v>
+        <v>-3.1732</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3934</v>
+        <v>0.1514</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3862</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7779</v>
+        <v>-0.8068</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4966</v>
+        <v>-0.8071</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2813</v>
+        <v>0.0004</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5712</v>
+        <v>-0.8568</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5712</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5638</v>
+        <v>-3.5443</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9502</v>
+        <v>-2.8055</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.514</v>
+        <v>-0.7388</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5124</v>
+        <v>-3.9046</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9789</v>
+        <v>-5.4893</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5336</v>
+        <v>1.5847</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6955</v>
+        <v>-2.0484</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5734</v>
+        <v>-2.6611</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1221</v>
+        <v>0.6127</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.2079</v>
+        <v>-1.8562</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.5522</v>
+        <v>-2.8282</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6556999999999999</v>
+        <v>0.972</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5792</v>
+        <v>1.5446</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1417</v>
+        <v>-1.0758</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1855</v>
+        <v>-0.6485</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0438</v>
+        <v>-0.4272</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8415</v>
+        <v>0.8568</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.8568</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8753</v>
+        <v>-4.6676</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0124</v>
+        <v>-1.8185</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8629</v>
+        <v>-2.849</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9046</v>
+        <v>-3.1629</v>
       </c>
       <c r="H22" t="n">
-        <v>-5.4893</v>
+        <v>-1.5036</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5847</v>
+        <v>-1.6593</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.0484</v>
+        <v>0.3208</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.6611</v>
+        <v>1.0487</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6127</v>
+        <v>-0.7279</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8562</v>
+        <v>-3.4837</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.8282</v>
+        <v>-2.5522</v>
       </c>
       <c r="O22" t="n">
-        <v>0.972</v>
+        <v>-0.9314</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4068</v>
+        <v>-0.462</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8554</v>
+        <v>-0.5175</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5514</v>
+        <v>0.0554</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8568</v>
+        <v>-0.6565</v>
       </c>
       <c r="W22" t="n">
-        <v>0.8568</v>
+        <v>-0.6565</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.267</v>
+        <v>-4.7263</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6672</v>
+        <v>-2.9775</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5998</v>
+        <v>-1.7488</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9783</v>
@@ -2248,13 +2248,13 @@
         <v>2.7031</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5131</v>
+        <v>-0.9724</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3866</v>
+        <v>-0.6969</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1265</v>
+        <v>-0.2755</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5133</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9778</v>
+        <v>-4.8504</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1288</v>
+        <v>-0.1874</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.849</v>
+        <v>-4.663</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1629</v>
+        <v>-1.5124</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5036</v>
+        <v>-0.9789</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6593</v>
+        <v>-0.5336</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3208</v>
+        <v>1.6955</v>
       </c>
       <c r="K24" t="n">
-        <v>1.0487</v>
+        <v>1.5734</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7279</v>
+        <v>0.1221</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.4837</v>
+        <v>-3.2079</v>
       </c>
       <c r="N24" t="n">
         <v>-2.5522</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9314</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R24" t="n">
         <v>0.5792</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7723</v>
+        <v>-0.1449</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8277</v>
+        <v>0.0479</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0554</v>
+        <v>-0.1928</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.6565</v>
+        <v>-1.8415</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="25">
@@ -2362,7 +2362,7 @@
         <v>-22.7693</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.089</v>
+        <v>-9.088899999999999</v>
       </c>
       <c r="F25" t="n">
         <v>-13.6803</v>
@@ -2377,7 +2377,7 @@
         <v>4.826300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>5.6643</v>
+        <v>5.664299999999999</v>
       </c>
       <c r="K25" t="n">
         <v>-1.0274</v>
@@ -2404,13 +2404,13 @@
         <v>14.4807</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.2066</v>
+        <v>-6.2065</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.554</v>
+        <v>-4.553999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.6526</v>
+        <v>-1.6524</v>
       </c>
       <c r="V25" t="n">
         <v>-3.5978</v>
